--- a/光伏配储项目/电价数据/2026/竹园站.xlsx
+++ b/光伏配储项目/电价数据/2026/竹园站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76518</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5748300000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5222599999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44444</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13212</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10726</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12351</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11334</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13653</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11399</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.1676</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14341</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.05691</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.03539</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10471</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15391</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21741</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.19328</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24878</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.09944</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.19744</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21788</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.67134</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55971</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.59285</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.40185</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6342899999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46966</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44786</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58272</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48456</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.64837</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.83275</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64446</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.66091</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8176</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.24238</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6974199999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6040399999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.86424</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65754</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65935</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.63029</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48153</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42576</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7145</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.756</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.79474</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.52505</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.85129</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5348200000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50513</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51133</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4884</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49925</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60093</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7400800000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52751</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.18016</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.07144</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41702</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7723</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.25692</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.81757</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.54334</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14659</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.52922</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.61734</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.73511</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.7699600000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.66039</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.80398</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.65032</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.91018</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79018</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.74705</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.6880700000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6113500000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77727</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.6037100000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06211</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66592</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43816</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33458</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51725</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54051</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26955</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48128</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52295</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49387</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.8017000000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.55835</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5789800000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.65198</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7646799999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57537</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.51088</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5450199999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49714</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47908</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46491</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34239</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43324</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46076</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.8593200000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.7137100000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.11114</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10822</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17884</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19361</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.2406</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5442100000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07507</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21993</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23878</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20393</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26759</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12205</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.6325499999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.65971</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30011</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25935</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05497</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04459</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04228</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03586</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04517</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04326</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04188</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21821</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04104</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04688000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.004059999999999999</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.02146</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.16011</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05951</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11619</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35064</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68168</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09951</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00383</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04414</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04776</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20006</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33549</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31773</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27133</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17251</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17104</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15953</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21411</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79092</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7811</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92057</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86673</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29885</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8919199999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6325299999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19148</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87098</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5420499999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33527</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5351399999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7946</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52961</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77663</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78042</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87722</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87576</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49654</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4043</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21141</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87903</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62624</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53943</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45641</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5857599999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42715</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59572</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60189</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6629700000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47553</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5824600000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8811599999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63212</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8813500000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86388</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86626</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45165</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91992</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46508</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46759</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49907</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16639</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26275</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19903</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19479</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5951000000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89003</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33241</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13941</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6986599999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78907</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6451699999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57811</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43957</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43683</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43377</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44943</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49504</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.20756</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63564</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.7363999999999999</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.70404</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.24834</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69928</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.82594</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.75718</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.80563</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5789500000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7522300000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46411</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43662</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32351</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.19229</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16798</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.6461699999999999</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.34155</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.29867</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15143</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.16228</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15162</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16094</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.22342</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.16044</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.18351</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.18494</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16698</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44262</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34843</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53687</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20282</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24955</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24254</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.45603</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35984</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.6133200000000001</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24963</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.56152</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12648</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43681</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70924</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.53327</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25992</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2848</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77449</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3436</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20151</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22499</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.8644299999999999</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.86085</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8585499999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.8468300000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43958</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64897</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60505</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5826399999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46541</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67325</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46218</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82559</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.13103</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35978</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53862</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49464</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44709</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55762</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47594</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49574</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.64367</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6557200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44189</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49397</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51092</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54486</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6952699999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7285</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67611</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8121499999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52354</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.82982</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7699</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6282799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67464</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48169</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46771</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5567000000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43003</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21137</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11964</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18025</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.85699</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36475</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13927</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04302</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17191</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18383</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22919</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34947</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25224</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23786</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16357</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20221</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01855</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03048</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11538</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01856</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03877000000000001</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00725</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03309</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02852</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04647</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01822</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18704</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04867</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03354</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04881</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04843</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18431</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19299</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12579</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5657799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2299</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25847</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21301</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23874</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21951</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14454</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6076900000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64695</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58088</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11668</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17772</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10815</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11808</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.09068999999999999</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16956</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02733</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10932</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.12022</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13896</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02169</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09156</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10553</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10365</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.47112</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32307</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5597799999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47921</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14279</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3283</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62436</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.58724</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.51175</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49683</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5069900000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.6305599999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36745</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41113</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5416599999999999</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.46144</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51591</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58316</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58631</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5286799999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5109900000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51985</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.69464</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86303</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5826699999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37228</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22994</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.18438</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16419</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04465</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22289</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01201</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26754</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17445</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06672</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06032</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08109000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17958</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08866</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16343</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.2146</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43033</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35997</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86602</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47114</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.25035</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11453</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.43531</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.83253</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.48282</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00398</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04855</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02023</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.08502</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.10397</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49839</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.57956</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35944</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61429</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25821</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14413</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20614</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23162</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15047</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04654999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04177</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07861</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06309000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09684999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17055</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19615</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12061</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12417</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05529999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11747</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18526</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23678</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24362</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20354</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4671</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36623</v>
       </c>
     </row>
   </sheetData>
